--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>153872.05</v>
+        <v>154690.6</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>50387.41</v>
+        <v>50321.79</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7797.59</v>
+        <v>7849.96</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>66626.96000000001</v>
+        <v>67506.00999999999</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>62871.94</v>
+        <v>63261.21</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>40568.04</v>
+        <v>40809.78</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>417442.81</v>
+        <v>405227.73</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>48135.83</v>
+        <v>48768.71</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>253601.02</v>
+        <v>257242.59</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>19620.85</v>
+        <v>19778.86</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/lib-gral-bdo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2777-884-CM25</t>
+          <t>1562-276-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>154690.6</v>
+        <v>24140.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3944-345-CM25</t>
+          <t>2777-884-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>50321.79</v>
+        <v>154690.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1398-2804-CM25</t>
+          <t>3944-345-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.091.500-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>RAYEN SALUD SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7849.96</v>
+        <v>50321.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1562-19-CM26</t>
+          <t>1398-2804-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>67506.00999999999</v>
+        <v>7849.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2677-36-CM26</t>
+          <t>1562-19-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>63261.21</v>
+        <v>67506.00999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1398-187-CM26</t>
+          <t>2677-36-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>RAYEN SALUD SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>40809.78</v>
+        <v>63261.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1743-66-CM26</t>
+          <t>1398-187-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>405227.73</v>
+        <v>40809.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>598-17-CM26</t>
+          <t>1743-66-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>48768.71</v>
+        <v>405227.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3598-440-CM26</t>
+          <t>598-17-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>257242.59</v>
+        <v>48768.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1529-168-CM26</t>
+          <t>3598-440-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,6 +1118,67 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
+        <v>257242.59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1529-168-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>19778.86</v>
       </c>
     </row>
